--- a/artfynd/A 8987-2025 artfynd.xlsx
+++ b/artfynd/A 8987-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189696</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189689</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189688</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189687</t>
         </is>
       </c>
     </row>
@@ -1365,6 +1395,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189690</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189691</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189692</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,6 +1773,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189693</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1847,8 +1897,25 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135189695</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 8987-2025 artfynd.xlsx
+++ b/artfynd/A 8987-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135189694</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135189696</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135189689</v>
       </c>
       <c r="B4" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135189688</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135189687</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>135189690</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>135189691</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>135189692</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>135189693</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>135189695</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 8987-2025 artfynd.xlsx
+++ b/artfynd/A 8987-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135189694</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135189696</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135189689</v>
       </c>
       <c r="B4" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
